--- a/pdf2img/tabel/table_12.xlsx
+++ b/pdf2img/tabel/table_12.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L112"/>
+  <dimension ref="A1:N82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,6 +452,12 @@
       </c>
       <c r="L1" t="n">
         <v>11</v>
+      </c>
+      <c r="M1" t="n">
+        <v>12</v>
+      </c>
+      <c r="N1" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="2">
@@ -479,14 +485,20 @@
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Per,31|Desember,2025</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr"/>
+          <t>[Per,31/Desember;2025</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>dan'31/Desember,2024</t>
+        </is>
+      </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
@@ -497,21 +509,35 @@
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>dan'3</t>
+          <t>{</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>1|Desember,2024</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
+          <t>datam</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>jutaan</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>ruplah</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>}</t>
+        </is>
+      </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
@@ -519,33 +545,23 @@
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>(</t>
+          <t>No.</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>dalam</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>jutaan</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>ruptah</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>}</t>
-        </is>
-      </c>
+          <t>31-Des-24</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
@@ -553,18 +569,16 @@
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>No,</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>31-Des-24</t>
-        </is>
-      </c>
+          <t>ASET</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
@@ -575,15 +589,25 @@
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ASET</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
+          <t>1.</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>|Kas</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>374523</t>
+        </is>
+      </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
@@ -593,23 +617,17 @@
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>1.</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>|Kas</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>374,523</t>
-        </is>
-      </c>
+          <t>.</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr"/>
@@ -619,176 +637,218 @@
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>.</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
+          <t>2.</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>|Penempatan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>pada</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Bank</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>14.711.234</t>
+        </is>
+      </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2.</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>|Penempatan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>pada</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Bank</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Indonesia</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>14.711.234</t>
-        </is>
-      </c>
+          <t>.361.</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>361.</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
+          <t>3.</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>|Penempatan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>pada</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>lain</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>1.410.942</t>
+        </is>
+      </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>3.</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>|Penempatan</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>pada</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>bank</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>lain</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>1.410.942</t>
-        </is>
-      </c>
+          <t>S11.</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Si.</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
+          <t>4.</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>|Tagihan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>spot</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>dan</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>derivatif/forward</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>4,</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr"/>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
+          <t>5.</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>|Surat</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>berharga</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>yang</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>dimiliki</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>8.189.413</t>
+        </is>
+      </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>|Tagihan</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>spot</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>dan</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>derivatif/forward</t>
-        </is>
-      </c>
+          <t>874.</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr"/>
@@ -797,68 +857,162 @@
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
+          <t>6.</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>|Surat</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>berharga</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>yang</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>dijual</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>dengan</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>janji</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>dibeli</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>kembali</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>{repo)</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>400,000</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>5.</t>
+          <t>7.</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>|Surat</t>
+          <t>|Tagihan</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
+          <t>atas</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>surat</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
           <t>berharga</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>dimiliki</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>8.198.413</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>yang</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>dibeli</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>dengan</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>janji</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>dijual</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>kembali</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>(reverse</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>repo)</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>yang</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr"/>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
+          <t>8.</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>|Tagihan</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>akseptasi</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>163.822</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr"/>
@@ -867,11 +1021,13 @@
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>874.</t>
+          <t>.</t>
         </is>
       </c>
       <c r="B19" t="inlineStr"/>
@@ -885,65 +1041,49 @@
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>6.</t>
+          <t>9.</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>|Surat</t>
+          <t>|Kredit</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>berharga</t>
+          <t>yang</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>dijual</t>
+          <t>diberikan</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>dengan</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>janji</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>dibeli</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>kembali</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>(repo)</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>406.000</t>
-        </is>
-      </c>
+          <t>106.532.459</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>yang</t>
+          <t>L1561,</t>
         </is>
       </c>
       <c r="B21" t="inlineStr"/>
@@ -957,81 +1097,53 @@
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>7.</t>
+          <t>10.</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>|Tagihan</t>
+          <t>|Pembiayaan</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>atas</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>surat</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>berharga</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>dibeti</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>dengan</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>janji</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>dijual</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>kembali</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>(reverse</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>repo)</t>
-        </is>
-      </c>
+          <t>syariah</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>yang</t>
+          <t>11.</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr"/>
+          <t>|Penyertaan</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>modal</t>
+        </is>
+      </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr"/>
@@ -1041,26 +1153,28 @@
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>8.</t>
+          <t>12.</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>|Tagihan</t>
+          <t>|Aset</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>akseptasi</t>
+          <t>keuangan</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>463.822</t>
+          <t>lainnya</t>
         </is>
       </c>
       <c r="E24" t="inlineStr"/>
@@ -1071,47 +1185,83 @@
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>.</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr"/>
-      <c r="C25" t="inlineStr"/>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
+          <t>13.</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>[Cadangan</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>kerugian</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>penurunan</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>aset</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>keuangan</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>-/-</t>
+        </is>
+      </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>9,</t>
+          <t>a.</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>|Kredit</t>
+          <t>Surat</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>diberikan</t>
+          <t>berharga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>106.632.459</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr"/>
+          <t>yang</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>dimiliki</t>
+        </is>
+      </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr"/>
@@ -1119,32 +1269,64 @@
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
+          <t>b.</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Kredit</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
           <t>yang</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr"/>
-      <c r="C27" t="inlineStr"/>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr"/>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>diberikan</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>dan</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>pembiayaan</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>syariah</t>
+        </is>
+      </c>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>151,</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr"/>
+          <t>¢.</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Lainnya</t>
+        </is>
+      </c>
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr"/>
@@ -1155,24 +1337,30 @@
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>10.</t>
+          <t>14.</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>|Pembiayaan</t>
+          <t>|Aset</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>syariah</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr"/>
+          <t>tidak</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>berwujud</t>
+        </is>
+      </c>
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr"/>
@@ -1181,37 +1369,53 @@
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>11,</t>
+          <t>Akumulasi</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>|Penyertaan</t>
+          <t>amortisasi</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>moda!</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr"/>
+          <t>aset</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>tidak</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>berwujud</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>-/</t>
+        </is>
+      </c>
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>12.</t>
+          <t>15.</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1221,15 +1425,19 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>keuangan</t>
+          <t>tetap</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>lainnya</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr"/>
+          <t>dan</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>inventaris</t>
+        </is>
+      </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr"/>
@@ -1237,36 +1445,38 @@
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>13.</t>
+          <t>Akumulasi</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>|Cadangan</t>
+          <t>penyusutan</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>kerugian</t>
+          <t>aset</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>nilai</t>
+          <t>tetap</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>aset</t>
+          <t>dan</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>keuangan</t>
+          <t>inventaris</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -1279,16 +1489,30 @@
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>penurunan</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr"/>
-      <c r="C33" t="inlineStr"/>
-      <c r="D33" t="inlineStr"/>
+          <t>16,</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>|Aset</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>produktif</t>
+        </is>
+      </c>
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr"/>
@@ -1297,6 +1521,8 @@
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1306,24 +1532,16 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Surat</t>
+          <t>Properti</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>berharga</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>yang</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>dimitiki</t>
-        </is>
-      </c>
+          <t>terbengkalai</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr"/>
@@ -1331,6 +1549,8 @@
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1340,44 +1560,50 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Kredit</t>
+          <t>Agunan</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>diberikan</t>
+          <t>yang</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>dan</t>
+          <t>diambil</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>pembiayaan</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>syariah</t>
-        </is>
-      </c>
+          <t>alih</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>yang</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr"/>
-      <c r="C36" t="inlineStr"/>
+          <t>¢.</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Rekening</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>tunda</t>
+        </is>
+      </c>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr"/>
@@ -1387,15 +1613,25 @@
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Lainnya</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr"/>
-      <c r="C37" t="inlineStr"/>
+          <t>d.</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Aset</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>antarkantor</t>
+        </is>
+      </c>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr"/>
@@ -1405,15 +1641,25 @@
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>c,</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr"/>
-      <c r="C38" t="inlineStr"/>
+          <t>17.</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>|Aset</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>lainnya</t>
+        </is>
+      </c>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr"/>
@@ -1423,28 +1669,22 @@
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>14.</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>|Aset</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>tidak</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>berwujud</t>
-        </is>
-      </c>
+          <t>ASET</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr"/>
+      <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr"/>
@@ -1453,21 +1693,23 @@
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>amortisasi</t>
+          <t>LIABILITAS</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>berwujud</t>
+          <t>DAN</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>-/-</t>
+          <t>EKUITAS</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
@@ -1479,23 +1721,17 @@
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Akumulasi</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>aset</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>tidak</t>
-        </is>
-      </c>
+          <t>LIABILITAS</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr"/>
+      <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr"/>
@@ -1505,33 +1741,23 @@
       <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>15.</t>
+          <t>LBNS</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>|Aset</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>tetap</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>dan</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>inventaris</t>
-        </is>
-      </c>
+          <t>Giro</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr"/>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr"/>
       <c r="H42" t="inlineStr"/>
@@ -1539,70 +1765,38 @@
       <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Akumulasi</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>penyusutan</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>aset</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>tetap</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>dan</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>inventaris</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>-/-</t>
-        </is>
-      </c>
+          <t>Tabungan</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr"/>
+      <c r="C43" t="inlineStr"/>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr"/>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr"/>
       <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>16,</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>|Aset</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>produktif</t>
-        </is>
-      </c>
+          <t>Deposito</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr"/>
+      <c r="C44" t="inlineStr"/>
+      <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr"/>
@@ -1611,19 +1805,25 @@
       <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Properti</t>
+          <t>GNP</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>terbengkalai</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr"/>
+          <t>Uang</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>elektronik</t>
+        </is>
+      </c>
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr"/>
@@ -1633,16 +1833,30 @@
       <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>a.</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr"/>
-      <c r="C46" t="inlineStr"/>
-      <c r="D46" t="inlineStr"/>
+          <t>Liabilitas</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>kepada</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Bank</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
       <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr"/>
@@ -1651,26 +1865,28 @@
       <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>b.</t>
+          <t>Liabilitas</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Agunan</t>
+          <t>kepada</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>diambil</t>
+          <t>bank</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>alih</t>
+          <t>lain</t>
         </is>
       </c>
       <c r="E47" t="inlineStr"/>
@@ -1681,17 +1897,35 @@
       <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>yang</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr"/>
-      <c r="C48" t="inlineStr"/>
-      <c r="D48" t="inlineStr"/>
-      <c r="E48" t="inlineStr"/>
+          <t>Liabilitas</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>spot</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>dan</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>derivatif/</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>forward</t>
+        </is>
+      </c>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr"/>
       <c r="H48" t="inlineStr"/>
@@ -1699,37 +1933,85 @@
       <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Rekening</t>
+          <t>Liabilitas</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>tunda</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr"/>
-      <c r="D49" t="inlineStr"/>
-      <c r="E49" t="inlineStr"/>
-      <c r="F49" t="inlineStr"/>
-      <c r="G49" t="inlineStr"/>
-      <c r="H49" t="inlineStr"/>
-      <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
+          <t>atas</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>surat</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>berharga</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>yang</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>dijual</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>dengan</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>janji</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>dibeli</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>kembali</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>{repo)</t>
+        </is>
+      </c>
       <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>c.</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr"/>
-      <c r="C50" t="inlineStr"/>
+          <t>9.</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>|Liabilitas</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>akseptasi</t>
+        </is>
+      </c>
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr"/>
@@ -1739,25 +2021,35 @@
       <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>d.</t>
+          <t>10,</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Aset</t>
+          <t>|Surat</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>antarkantor</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr"/>
-      <c r="E51" t="inlineStr"/>
+          <t>berharga</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>yang</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>diterbitkan</t>
+        </is>
+      </c>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr"/>
       <c r="H51" t="inlineStr"/>
@@ -1765,24 +2057,30 @@
       <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>17.</t>
+          <t>11.</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>|Aset</t>
+          <t>|Pinjaman/pembiayaan</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>lainnya</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr"/>
+          <t>yang</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>diterima</t>
+        </is>
+      </c>
       <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr"/>
@@ -1791,20 +2089,30 @@
       <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>12.</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>ASET</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr"/>
-      <c r="D53" t="inlineStr"/>
+          <t>|</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Setoran</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>jaminan</t>
+        </is>
+      </c>
       <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr"/>
@@ -1813,21 +2121,23 @@
       <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>LIABILITAS</t>
+          <t>13.</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>DAN</t>
+          <t>|Liabilitas</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>EKUITAS</t>
+          <t>antarkantor</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
@@ -1839,15 +2149,25 @@
       <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>LIABILITAS</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr"/>
-      <c r="C55" t="inlineStr"/>
+          <t>14.</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>|Liabilitas</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>lainnya</t>
+        </is>
+      </c>
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr"/>
@@ -1857,41 +2177,65 @@
       <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>=</t>
+          <t>15,</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>PNOAPON</t>
+          <t>|Kepentingan</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Giro</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr"/>
-      <c r="E56" t="inlineStr"/>
-      <c r="F56" t="inlineStr"/>
+          <t>minoritas</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>(minority</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>inferest)</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="G56" t="inlineStr"/>
       <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr"/>
       <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Tabungan</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr"/>
-      <c r="C57" t="inlineStr"/>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>LIABILITAS</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>133.244.905</t>
+        </is>
+      </c>
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr"/>
@@ -1901,11 +2245,13 @@
       <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Deposito</t>
+          <t>EKUITAS</t>
         </is>
       </c>
       <c r="B58" t="inlineStr"/>
@@ -1919,15 +2265,25 @@
       <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>elektrontk</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr"/>
-      <c r="C59" t="inlineStr"/>
+          <t>16.</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>|Modal</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>disetor</t>
+        </is>
+      </c>
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr"/>
@@ -1937,16 +2293,30 @@
       <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Uang</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr"/>
-      <c r="C60" t="inlineStr"/>
-      <c r="D60" t="inlineStr"/>
+          <t>a.</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Modal</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>dasar</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>£.300,000</t>
+        </is>
+      </c>
       <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr"/>
@@ -1955,28 +2325,18 @@
       <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Liabilitas</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>kepada</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Bank</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>tndonesia</t>
-        </is>
-      </c>
+          <t>.300.</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr"/>
+      <c r="C61" t="inlineStr"/>
+      <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr"/>
@@ -1985,58 +2345,62 @@
       <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Liabilitas</t>
+          <t>b.</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>kepada</t>
+          <t>Modal</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>bank</t>
+          <t>yang</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>lain</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr"/>
-      <c r="F62" t="inlineStr"/>
-      <c r="G62" t="inlineStr"/>
+          <t>belum</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>disetor</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>-/-</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>{3.961.461</t>
+        </is>
+      </c>
       <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr"/>
       <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr"/>
       <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr"/>
+      <c r="N62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Liabilitas</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>spot</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>dan</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>derivatif/forward</t>
-        </is>
-      </c>
+          <t>.961.</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr"/>
+      <c r="C63" t="inlineStr"/>
+      <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr"/>
@@ -2045,83 +2409,87 @@
       <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr"/>
       <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Liabilitas</t>
+          <t>¢.</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>atas</t>
+          <t>Saham</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>surat</t>
+          <t>yang</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>berharga</t>
+          <t>dibeli</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>yang</t>
+          <t>kembali</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>dijua!</t>
+          <t>(freasury</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>dengan</t>
+          <t>stock}</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>janji</t>
+          <t>-i-</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>dibeli</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>kembali</t>
-        </is>
-      </c>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t>/repo)</t>
-        </is>
-      </c>
+          <t>.</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
       <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>9.</t>
+          <t>17.</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>|Liabilitas</t>
+          <t>|</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>akseptasi</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr"/>
-      <c r="E65" t="inlineStr"/>
+          <t>Tambahan</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>modal</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>disetor</t>
+        </is>
+      </c>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr"/>
       <c r="H65" t="inlineStr"/>
@@ -2129,26 +2497,28 @@
       <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>10,</t>
+          <t>a.</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>|Surat</t>
+          <t>Agio</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>berharga</t>
+          <t>.364.</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>diterbitkan</t>
+          <t>8.364.829</t>
         </is>
       </c>
       <c r="E66" t="inlineStr"/>
@@ -2159,16 +2529,30 @@
       <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr"/>
       <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>yang</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr"/>
-      <c r="C67" t="inlineStr"/>
-      <c r="D67" t="inlineStr"/>
+          <t>b.</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Disagio</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>-/-</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr"/>
@@ -2177,17 +2561,35 @@
       <c r="J67" t="inlineStr"/>
       <c r="K67" t="inlineStr"/>
       <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr"/>
+      <c r="N67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>|Pinjaman/pembiayaan</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr"/>
-      <c r="C68" t="inlineStr"/>
-      <c r="D68" t="inlineStr"/>
-      <c r="E68" t="inlineStr"/>
+          <t>¢.</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Dana</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>setoran</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>modal</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>2.144.516</t>
+        </is>
+      </c>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr"/>
       <c r="H68" t="inlineStr"/>
@@ -2195,23 +2597,17 @@
       <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr"/>
       <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr"/>
+      <c r="N68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>11.</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>yang</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>diterima</t>
-        </is>
-      </c>
+          <t>144,</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr"/>
+      <c r="C69" t="inlineStr"/>
       <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr"/>
       <c r="F69" t="inlineStr"/>
@@ -2221,23 +2617,21 @@
       <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr"/>
       <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr"/>
+      <c r="N69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>12.</t>
+          <t>d.</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>|Setoran</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>jaminan</t>
-        </is>
-      </c>
+          <t>Lainnya</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr"/>
       <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr"/>
       <c r="F70" t="inlineStr"/>
@@ -2247,24 +2641,30 @@
       <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr"/>
       <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr"/>
+      <c r="N70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>13.</t>
+          <t>18.</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>|Liabilitas</t>
+          <t>|Penghasilan</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>antarkantor</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr"/>
+          <t>komprehensif</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>lain</t>
+        </is>
+      </c>
       <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr"/>
@@ -2273,23 +2673,21 @@
       <c r="J71" t="inlineStr"/>
       <c r="K71" t="inlineStr"/>
       <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr"/>
+      <c r="N71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>14.</t>
+          <t>a.</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>|Liabilitas</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>lainnya</t>
-        </is>
-      </c>
+          <t>Keuntungan</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr"/>
       <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr"/>
@@ -2299,15 +2697,25 @@
       <c r="J72" t="inlineStr"/>
       <c r="K72" t="inlineStr"/>
       <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr"/>
+      <c r="N72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>15,</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr"/>
-      <c r="C73" t="inlineStr"/>
+          <t>b.</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Kerugian</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>-/-</t>
+        </is>
+      </c>
       <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr"/>
       <c r="F73" t="inlineStr"/>
@@ -2317,28 +2725,22 @@
       <c r="J73" t="inlineStr"/>
       <c r="K73" t="inlineStr"/>
       <c r="L73" t="inlineStr"/>
+      <c r="M73" t="inlineStr"/>
+      <c r="N73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>|Kepentingan</t>
+          <t>19.</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>minoritas</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>(minority</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>interest)</t>
-        </is>
-      </c>
+          <t>|Cadangan</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr"/>
+      <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr"/>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr"/>
@@ -2347,17 +2749,35 @@
       <c r="J74" t="inlineStr"/>
       <c r="K74" t="inlineStr"/>
       <c r="L74" t="inlineStr"/>
+      <c r="M74" t="inlineStr"/>
+      <c r="N74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr"/>
-      <c r="C75" t="inlineStr"/>
-      <c r="D75" t="inlineStr"/>
-      <c r="E75" t="inlineStr"/>
+          <t>a.</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Cadangan</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>umum</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>132.600</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>131.600</t>
+        </is>
+      </c>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="inlineStr"/>
       <c r="H75" t="inlineStr"/>
@@ -2365,25 +2785,35 @@
       <c r="J75" t="inlineStr"/>
       <c r="K75" t="inlineStr"/>
       <c r="L75" t="inlineStr"/>
+      <c r="M75" t="inlineStr"/>
+      <c r="N75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>b.</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>LIABILITAS</t>
+          <t>Cadangan</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>133.244.3905</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr"/>
-      <c r="E76" t="inlineStr"/>
+          <t>tujuan</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr"/>
       <c r="H76" t="inlineStr"/>
@@ -2391,14 +2821,20 @@
       <c r="J76" t="inlineStr"/>
       <c r="K76" t="inlineStr"/>
       <c r="L76" t="inlineStr"/>
+      <c r="M76" t="inlineStr"/>
+      <c r="N76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>EKUITAS</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr"/>
+          <t>20.</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>|Labalrugi</t>
+        </is>
+      </c>
       <c r="C77" t="inlineStr"/>
       <c r="D77" t="inlineStr"/>
       <c r="E77" t="inlineStr"/>
@@ -2409,25 +2845,35 @@
       <c r="J77" t="inlineStr"/>
       <c r="K77" t="inlineStr"/>
       <c r="L77" t="inlineStr"/>
+      <c r="M77" t="inlineStr"/>
+      <c r="N77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>16.</t>
+          <t>a.</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>|Modal</t>
+          <t>Tahun-tahun</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>disetor</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr"/>
-      <c r="E78" t="inlineStr"/>
+          <t>laly</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>3.457.984</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>3.3986.,001</t>
+        </is>
+      </c>
       <c r="F78" t="inlineStr"/>
       <c r="G78" t="inlineStr"/>
       <c r="H78" t="inlineStr"/>
@@ -2435,25 +2881,35 @@
       <c r="J78" t="inlineStr"/>
       <c r="K78" t="inlineStr"/>
       <c r="L78" t="inlineStr"/>
+      <c r="M78" t="inlineStr"/>
+      <c r="N78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Mada!</t>
+          <t>b.</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>dasar</t>
+          <t>Tahun</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>§.300,000</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr"/>
-      <c r="E79" t="inlineStr"/>
+          <t>berjalan</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>20.975</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>25573</t>
+        </is>
+      </c>
       <c r="F79" t="inlineStr"/>
       <c r="G79" t="inlineStr"/>
       <c r="H79" t="inlineStr"/>
@@ -2461,34 +2917,74 @@
       <c r="J79" t="inlineStr"/>
       <c r="K79" t="inlineStr"/>
       <c r="L79" t="inlineStr"/>
+      <c r="M79" t="inlineStr"/>
+      <c r="N79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>a,</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr"/>
-      <c r="C80" t="inlineStr"/>
-      <c r="D80" t="inlineStr"/>
-      <c r="E80" t="inlineStr"/>
-      <c r="F80" t="inlineStr"/>
-      <c r="G80" t="inlineStr"/>
+          <t>¢.</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Dividen</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>yang</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>dibayarkan</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>-/-</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="H80" t="inlineStr"/>
       <c r="I80" t="inlineStr"/>
       <c r="J80" t="inlineStr"/>
       <c r="K80" t="inlineStr"/>
       <c r="L80" t="inlineStr"/>
+      <c r="M80" t="inlineStr"/>
+      <c r="N80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>300;</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr"/>
-      <c r="C81" t="inlineStr"/>
-      <c r="D81" t="inlineStr"/>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>EKUITAS</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>17.065.119</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>16.939.270</t>
+        </is>
+      </c>
       <c r="E81" t="inlineStr"/>
       <c r="F81" t="inlineStr"/>
       <c r="G81" t="inlineStr"/>
@@ -2497,36 +2993,38 @@
       <c r="J81" t="inlineStr"/>
       <c r="K81" t="inlineStr"/>
       <c r="L81" t="inlineStr"/>
+      <c r="M81" t="inlineStr"/>
+      <c r="N81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>b.</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Moda!</t>
+          <t>LIABILITAS</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>belum</t>
+          <t>DAN</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>disetor</t>
+          <t>EKUITAS</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>-/-</t>
+          <t>163.825.380</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>{3.961.461</t>
+          <t>150.184.175</t>
         </is>
       </c>
       <c r="G82" t="inlineStr"/>
@@ -2535,754 +3033,8 @@
       <c r="J82" t="inlineStr"/>
       <c r="K82" t="inlineStr"/>
       <c r="L82" t="inlineStr"/>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>yang</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr"/>
-      <c r="C83" t="inlineStr"/>
-      <c r="D83" t="inlineStr"/>
-      <c r="E83" t="inlineStr"/>
-      <c r="F83" t="inlineStr"/>
-      <c r="G83" t="inlineStr"/>
-      <c r="H83" t="inlineStr"/>
-      <c r="I83" t="inlineStr"/>
-      <c r="J83" t="inlineStr"/>
-      <c r="K83" t="inlineStr"/>
-      <c r="L83" t="inlineStr"/>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>.961.</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr"/>
-      <c r="C84" t="inlineStr"/>
-      <c r="D84" t="inlineStr"/>
-      <c r="E84" t="inlineStr"/>
-      <c r="F84" t="inlineStr"/>
-      <c r="G84" t="inlineStr"/>
-      <c r="H84" t="inlineStr"/>
-      <c r="I84" t="inlineStr"/>
-      <c r="J84" t="inlineStr"/>
-      <c r="K84" t="inlineStr"/>
-      <c r="L84" t="inlineStr"/>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>¢.</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>Saham</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>yang</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>dibeli</t>
-        </is>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>kembali</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>(treasury</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>stock}</t>
-        </is>
-      </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>-/-</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr"/>
-      <c r="J85" t="inlineStr"/>
-      <c r="K85" t="inlineStr"/>
-      <c r="L85" t="inlineStr"/>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr"/>
-      <c r="C86" t="inlineStr"/>
-      <c r="D86" t="inlineStr"/>
-      <c r="E86" t="inlineStr"/>
-      <c r="F86" t="inlineStr"/>
-      <c r="G86" t="inlineStr"/>
-      <c r="H86" t="inlineStr"/>
-      <c r="I86" t="inlineStr"/>
-      <c r="J86" t="inlineStr"/>
-      <c r="K86" t="inlineStr"/>
-      <c r="L86" t="inlineStr"/>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>17,</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>|Tambahan</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>moda!</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>disetor</t>
-        </is>
-      </c>
-      <c r="E87" t="inlineStr"/>
-      <c r="F87" t="inlineStr"/>
-      <c r="G87" t="inlineStr"/>
-      <c r="H87" t="inlineStr"/>
-      <c r="I87" t="inlineStr"/>
-      <c r="J87" t="inlineStr"/>
-      <c r="K87" t="inlineStr"/>
-      <c r="L87" t="inlineStr"/>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>Agio</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>8.364.829</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr"/>
-      <c r="D88" t="inlineStr"/>
-      <c r="E88" t="inlineStr"/>
-      <c r="F88" t="inlineStr"/>
-      <c r="G88" t="inlineStr"/>
-      <c r="H88" t="inlineStr"/>
-      <c r="I88" t="inlineStr"/>
-      <c r="J88" t="inlineStr"/>
-      <c r="K88" t="inlineStr"/>
-      <c r="L88" t="inlineStr"/>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>a.</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr"/>
-      <c r="C89" t="inlineStr"/>
-      <c r="D89" t="inlineStr"/>
-      <c r="E89" t="inlineStr"/>
-      <c r="F89" t="inlineStr"/>
-      <c r="G89" t="inlineStr"/>
-      <c r="H89" t="inlineStr"/>
-      <c r="I89" t="inlineStr"/>
-      <c r="J89" t="inlineStr"/>
-      <c r="K89" t="inlineStr"/>
-      <c r="L89" t="inlineStr"/>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>364,</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr"/>
-      <c r="C90" t="inlineStr"/>
-      <c r="D90" t="inlineStr"/>
-      <c r="E90" t="inlineStr"/>
-      <c r="F90" t="inlineStr"/>
-      <c r="G90" t="inlineStr"/>
-      <c r="H90" t="inlineStr"/>
-      <c r="I90" t="inlineStr"/>
-      <c r="J90" t="inlineStr"/>
-      <c r="K90" t="inlineStr"/>
-      <c r="L90" t="inlineStr"/>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>b,</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>Disagio</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>-/-</t>
-        </is>
-      </c>
-      <c r="D91" t="inlineStr"/>
-      <c r="E91" t="inlineStr"/>
-      <c r="F91" t="inlineStr"/>
-      <c r="G91" t="inlineStr"/>
-      <c r="H91" t="inlineStr"/>
-      <c r="I91" t="inlineStr"/>
-      <c r="J91" t="inlineStr"/>
-      <c r="K91" t="inlineStr"/>
-      <c r="L91" t="inlineStr"/>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr"/>
-      <c r="C92" t="inlineStr"/>
-      <c r="D92" t="inlineStr"/>
-      <c r="E92" t="inlineStr"/>
-      <c r="F92" t="inlineStr"/>
-      <c r="G92" t="inlineStr"/>
-      <c r="H92" t="inlineStr"/>
-      <c r="I92" t="inlineStr"/>
-      <c r="J92" t="inlineStr"/>
-      <c r="K92" t="inlineStr"/>
-      <c r="L92" t="inlineStr"/>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>Dana</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>modal</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>2.144.516</t>
-        </is>
-      </c>
-      <c r="D93" t="inlineStr"/>
-      <c r="E93" t="inlineStr"/>
-      <c r="F93" t="inlineStr"/>
-      <c r="G93" t="inlineStr"/>
-      <c r="H93" t="inlineStr"/>
-      <c r="I93" t="inlineStr"/>
-      <c r="J93" t="inlineStr"/>
-      <c r="K93" t="inlineStr"/>
-      <c r="L93" t="inlineStr"/>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>c.</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>setoran</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr"/>
-      <c r="D94" t="inlineStr"/>
-      <c r="E94" t="inlineStr"/>
-      <c r="F94" t="inlineStr"/>
-      <c r="G94" t="inlineStr"/>
-      <c r="H94" t="inlineStr"/>
-      <c r="I94" t="inlineStr"/>
-      <c r="J94" t="inlineStr"/>
-      <c r="K94" t="inlineStr"/>
-      <c r="L94" t="inlineStr"/>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>144,</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr"/>
-      <c r="C95" t="inlineStr"/>
-      <c r="D95" t="inlineStr"/>
-      <c r="E95" t="inlineStr"/>
-      <c r="F95" t="inlineStr"/>
-      <c r="G95" t="inlineStr"/>
-      <c r="H95" t="inlineStr"/>
-      <c r="I95" t="inlineStr"/>
-      <c r="J95" t="inlineStr"/>
-      <c r="K95" t="inlineStr"/>
-      <c r="L95" t="inlineStr"/>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>d.</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>Lainnya</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr"/>
-      <c r="D96" t="inlineStr"/>
-      <c r="E96" t="inlineStr"/>
-      <c r="F96" t="inlineStr"/>
-      <c r="G96" t="inlineStr"/>
-      <c r="H96" t="inlineStr"/>
-      <c r="I96" t="inlineStr"/>
-      <c r="J96" t="inlineStr"/>
-      <c r="K96" t="inlineStr"/>
-      <c r="L96" t="inlineStr"/>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>18.</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>|Penghasilan</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>komprehensif</t>
-        </is>
-      </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>lain</t>
-        </is>
-      </c>
-      <c r="E97" t="inlineStr"/>
-      <c r="F97" t="inlineStr"/>
-      <c r="G97" t="inlineStr"/>
-      <c r="H97" t="inlineStr"/>
-      <c r="I97" t="inlineStr"/>
-      <c r="J97" t="inlineStr"/>
-      <c r="K97" t="inlineStr"/>
-      <c r="L97" t="inlineStr"/>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>a.</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>Keuntungan</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr"/>
-      <c r="D98" t="inlineStr"/>
-      <c r="E98" t="inlineStr"/>
-      <c r="F98" t="inlineStr"/>
-      <c r="G98" t="inlineStr"/>
-      <c r="H98" t="inlineStr"/>
-      <c r="I98" t="inlineStr"/>
-      <c r="J98" t="inlineStr"/>
-      <c r="K98" t="inlineStr"/>
-      <c r="L98" t="inlineStr"/>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>b,</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>Kerugian</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>-/-</t>
-        </is>
-      </c>
-      <c r="D99" t="inlineStr"/>
-      <c r="E99" t="inlineStr"/>
-      <c r="F99" t="inlineStr"/>
-      <c r="G99" t="inlineStr"/>
-      <c r="H99" t="inlineStr"/>
-      <c r="I99" t="inlineStr"/>
-      <c r="J99" t="inlineStr"/>
-      <c r="K99" t="inlineStr"/>
-      <c r="L99" t="inlineStr"/>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>19.</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>|</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>Cadangan</t>
-        </is>
-      </c>
-      <c r="D100" t="inlineStr"/>
-      <c r="E100" t="inlineStr"/>
-      <c r="F100" t="inlineStr"/>
-      <c r="G100" t="inlineStr"/>
-      <c r="H100" t="inlineStr"/>
-      <c r="I100" t="inlineStr"/>
-      <c r="J100" t="inlineStr"/>
-      <c r="K100" t="inlineStr"/>
-      <c r="L100" t="inlineStr"/>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>a.</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>Cadangan</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>umum</t>
-        </is>
-      </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>132.600</t>
-        </is>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>131.600</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr"/>
-      <c r="G101" t="inlineStr"/>
-      <c r="H101" t="inlineStr"/>
-      <c r="I101" t="inlineStr"/>
-      <c r="J101" t="inlineStr"/>
-      <c r="K101" t="inlineStr"/>
-      <c r="L101" t="inlineStr"/>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>b.</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>Cadangan</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>tujuan</t>
-        </is>
-      </c>
-      <c r="D102" t="inlineStr"/>
-      <c r="E102" t="inlineStr"/>
-      <c r="F102" t="inlineStr"/>
-      <c r="G102" t="inlineStr"/>
-      <c r="H102" t="inlineStr"/>
-      <c r="I102" t="inlineStr"/>
-      <c r="J102" t="inlineStr"/>
-      <c r="K102" t="inlineStr"/>
-      <c r="L102" t="inlineStr"/>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr"/>
-      <c r="D103" t="inlineStr"/>
-      <c r="E103" t="inlineStr"/>
-      <c r="F103" t="inlineStr"/>
-      <c r="G103" t="inlineStr"/>
-      <c r="H103" t="inlineStr"/>
-      <c r="I103" t="inlineStr"/>
-      <c r="J103" t="inlineStr"/>
-      <c r="K103" t="inlineStr"/>
-      <c r="L103" t="inlineStr"/>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>20.</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>|Laba/rugi</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr"/>
-      <c r="D104" t="inlineStr"/>
-      <c r="E104" t="inlineStr"/>
-      <c r="F104" t="inlineStr"/>
-      <c r="G104" t="inlineStr"/>
-      <c r="H104" t="inlineStr"/>
-      <c r="I104" t="inlineStr"/>
-      <c r="J104" t="inlineStr"/>
-      <c r="K104" t="inlineStr"/>
-      <c r="L104" t="inlineStr"/>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>Tahun-tahun</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>lalu</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>3,457,984</t>
-        </is>
-      </c>
-      <c r="D105" t="inlineStr">
-        <is>
-          <t>3.396,001</t>
-        </is>
-      </c>
-      <c r="E105" t="inlineStr"/>
-      <c r="F105" t="inlineStr"/>
-      <c r="G105" t="inlineStr"/>
-      <c r="H105" t="inlineStr"/>
-      <c r="I105" t="inlineStr"/>
-      <c r="J105" t="inlineStr"/>
-      <c r="K105" t="inlineStr"/>
-      <c r="L105" t="inlineStr"/>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>a,</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr"/>
-      <c r="C106" t="inlineStr"/>
-      <c r="D106" t="inlineStr"/>
-      <c r="E106" t="inlineStr"/>
-      <c r="F106" t="inlineStr"/>
-      <c r="G106" t="inlineStr"/>
-      <c r="H106" t="inlineStr"/>
-      <c r="I106" t="inlineStr"/>
-      <c r="J106" t="inlineStr"/>
-      <c r="K106" t="inlineStr"/>
-      <c r="L106" t="inlineStr"/>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>b.</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>Tahun</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>berjalan</t>
-        </is>
-      </c>
-      <c r="D107" t="inlineStr">
-        <is>
-          <t>29.975</t>
-        </is>
-      </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>25.573</t>
-        </is>
-      </c>
-      <c r="F107" t="inlineStr"/>
-      <c r="G107" t="inlineStr"/>
-      <c r="H107" t="inlineStr"/>
-      <c r="I107" t="inlineStr"/>
-      <c r="J107" t="inlineStr"/>
-      <c r="K107" t="inlineStr"/>
-      <c r="L107" t="inlineStr"/>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>Dividen</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>dibayarkan</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>-/-</t>
-        </is>
-      </c>
-      <c r="D108" t="inlineStr"/>
-      <c r="E108" t="inlineStr"/>
-      <c r="F108" t="inlineStr"/>
-      <c r="G108" t="inlineStr"/>
-      <c r="H108" t="inlineStr"/>
-      <c r="I108" t="inlineStr"/>
-      <c r="J108" t="inlineStr"/>
-      <c r="K108" t="inlineStr"/>
-      <c r="L108" t="inlineStr"/>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>¢.</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>yang</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr"/>
-      <c r="D109" t="inlineStr"/>
-      <c r="E109" t="inlineStr"/>
-      <c r="F109" t="inlineStr"/>
-      <c r="G109" t="inlineStr"/>
-      <c r="H109" t="inlineStr"/>
-      <c r="I109" t="inlineStr"/>
-      <c r="J109" t="inlineStr"/>
-      <c r="K109" t="inlineStr"/>
-      <c r="L109" t="inlineStr"/>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr"/>
-      <c r="D110" t="inlineStr"/>
-      <c r="E110" t="inlineStr"/>
-      <c r="F110" t="inlineStr"/>
-      <c r="G110" t="inlineStr"/>
-      <c r="H110" t="inlineStr"/>
-      <c r="I110" t="inlineStr"/>
-      <c r="J110" t="inlineStr"/>
-      <c r="K110" t="inlineStr"/>
-      <c r="L110" t="inlineStr"/>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>EKUITAS</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>17.065.119</t>
-        </is>
-      </c>
-      <c r="D111" t="inlineStr">
-        <is>
-          <t>16.939.270</t>
-        </is>
-      </c>
-      <c r="E111" t="inlineStr"/>
-      <c r="F111" t="inlineStr"/>
-      <c r="G111" t="inlineStr"/>
-      <c r="H111" t="inlineStr"/>
-      <c r="I111" t="inlineStr"/>
-      <c r="J111" t="inlineStr"/>
-      <c r="K111" t="inlineStr"/>
-      <c r="L111" t="inlineStr"/>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>LIABILITAS</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>DAN</t>
-        </is>
-      </c>
-      <c r="D112" t="inlineStr">
-        <is>
-          <t>EKUITAS</t>
-        </is>
-      </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>163.825.380</t>
-        </is>
-      </c>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t>150.184.175</t>
-        </is>
-      </c>
-      <c r="G112" t="inlineStr"/>
-      <c r="H112" t="inlineStr"/>
-      <c r="I112" t="inlineStr"/>
-      <c r="J112" t="inlineStr"/>
-      <c r="K112" t="inlineStr"/>
-      <c r="L112" t="inlineStr"/>
+      <c r="M82" t="inlineStr"/>
+      <c r="N82" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
